--- a/tasks/finalpool/canvas-grades-gsheet-pdf-email/groundtruth_workspace/Grade_Dashboard_Reference.xlsx
+++ b/tasks/finalpool/canvas-grades-gsheet-pdf-email/groundtruth_workspace/Grade_Dashboard_Reference.xlsx
@@ -471,28 +471,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>55</v>
       </c>
       <c r="H2" t="n">
-        <v>85.5</v>
+        <v>78.2</v>
       </c>
       <c r="I2" t="n">
-        <v>79.2</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -502,28 +502,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>89.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>81.5</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="4">
@@ -533,28 +533,28 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" t="n">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
-        <v>18</v>
-      </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>54</v>
       </c>
       <c r="H4" t="n">
-        <v>81.5</v>
+        <v>66.7</v>
       </c>
       <c r="I4" t="n">
-        <v>76.8</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="5">
@@ -564,28 +564,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>90.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>82.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" t="n">
-        <v>88.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>80.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -626,28 +626,28 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
         <v>14</v>
       </c>
-      <c r="C7" t="n">
-        <v>16</v>
-      </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
       </c>
       <c r="H7" t="n">
-        <v>78.2</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
-        <v>74.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85.7</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="6">
@@ -724,7 +724,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Database Systems</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
     </row>

--- a/tasks/finalpool/canvas-grades-gsheet-pdf-email/groundtruth_workspace/Grade_Dashboard_Reference.xlsx
+++ b/tasks/finalpool/canvas-grades-gsheet-pdf-email/groundtruth_workspace/Grade_Dashboard_Reference.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,187 +467,683 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Advanced Data Science</t>
+          <t>Applied Analytics &amp; Algorithms (Fall 2013)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>364</v>
       </c>
       <c r="H2" t="n">
-        <v>78.2</v>
+        <v>53.3</v>
       </c>
       <c r="I2" t="n">
-        <v>76.09999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Applied Analytics &amp; Algorithms (Fall 2014)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>56</v>
+        <v>340</v>
       </c>
       <c r="H3" t="n">
-        <v>83.90000000000001</v>
+        <v>49.1</v>
       </c>
       <c r="I3" t="n">
-        <v>79.7</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2013)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>658</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>533</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="G4" t="n">
-        <v>54</v>
+        <v>1710</v>
       </c>
       <c r="H4" t="n">
-        <v>66.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>73.7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Database Systems</t>
+          <t>Biochemistry &amp; Bioinformatics (Fall 2014)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>138</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>421</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>341</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>634</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>1792</v>
       </c>
       <c r="H5" t="n">
-        <v>83.59999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="I5" t="n">
-        <v>80.59999999999999</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2013)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>535</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>69</v>
+        <v>1366</v>
       </c>
       <c r="H6" t="n">
-        <v>89.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I6" t="n">
-        <v>81.59999999999999</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Biochemistry &amp; Bioinformatics (Spring 2014)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>480</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>365</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>1204</v>
       </c>
       <c r="H7" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>77.40000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Creative Computing &amp; Culture (Fall 2014)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>372</v>
+      </c>
+      <c r="C8" t="n">
+        <v>395</v>
+      </c>
+      <c r="D8" t="n">
+        <v>344</v>
+      </c>
+      <c r="E8" t="n">
+        <v>325</v>
+      </c>
+      <c r="F8" t="n">
+        <v>562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Creative Computing &amp; Culture (Spring 2014)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>193</v>
+      </c>
+      <c r="C9" t="n">
+        <v>213</v>
+      </c>
+      <c r="D9" t="n">
+        <v>223</v>
+      </c>
+      <c r="E9" t="n">
+        <v>242</v>
+      </c>
+      <c r="F9" t="n">
+        <v>543</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1414</v>
+      </c>
+      <c r="H9" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data-Driven Design (Fall 2013)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>71</v>
+      </c>
+      <c r="C10" t="n">
+        <v>317</v>
+      </c>
+      <c r="D10" t="n">
+        <v>347</v>
+      </c>
+      <c r="E10" t="n">
+        <v>303</v>
+      </c>
+      <c r="F10" t="n">
+        <v>467</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1505</v>
+      </c>
+      <c r="H10" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data-Driven Design (Fall 2014)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>92</v>
+      </c>
+      <c r="C11" t="n">
+        <v>327</v>
+      </c>
+      <c r="D11" t="n">
+        <v>339</v>
+      </c>
+      <c r="E11" t="n">
+        <v>318</v>
+      </c>
+      <c r="F11" t="n">
+        <v>351</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1427</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data-Driven Design (Spring 2013)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>54</v>
+      </c>
+      <c r="C12" t="n">
+        <v>197</v>
+      </c>
+      <c r="D12" t="n">
+        <v>234</v>
+      </c>
+      <c r="E12" t="n">
+        <v>215</v>
+      </c>
+      <c r="F12" t="n">
+        <v>364</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1064</v>
+      </c>
+      <c r="H12" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data-Driven Design (Spring 2014)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50</v>
+      </c>
+      <c r="C13" t="n">
+        <v>179</v>
+      </c>
+      <c r="D13" t="n">
+        <v>217</v>
+      </c>
+      <c r="E13" t="n">
+        <v>186</v>
+      </c>
+      <c r="F13" t="n">
+        <v>312</v>
+      </c>
+      <c r="G13" t="n">
+        <v>944</v>
+      </c>
+      <c r="H13" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Environmental Economics &amp; Ethics (Fall 2013)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>181</v>
+      </c>
+      <c r="C14" t="n">
+        <v>309</v>
+      </c>
+      <c r="D14" t="n">
+        <v>176</v>
+      </c>
+      <c r="E14" t="n">
+        <v>86</v>
+      </c>
+      <c r="F14" t="n">
+        <v>75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>827</v>
+      </c>
+      <c r="H14" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>79.59999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Environmental Economics &amp; Ethics (Fall 2014)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>263</v>
+      </c>
+      <c r="C15" t="n">
+        <v>340</v>
+      </c>
+      <c r="D15" t="n">
+        <v>174</v>
+      </c>
+      <c r="E15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F15" t="n">
+        <v>69</v>
+      </c>
+      <c r="G15" t="n">
+        <v>934</v>
+      </c>
+      <c r="H15" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>81.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Environmental Economics &amp; Ethics (Spring 2014)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>116</v>
+      </c>
+      <c r="C16" t="n">
+        <v>189</v>
+      </c>
+      <c r="D16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62</v>
+      </c>
+      <c r="F16" t="n">
+        <v>49</v>
+      </c>
+      <c r="G16" t="n">
+        <v>536</v>
+      </c>
+      <c r="H16" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Foundations of Finance (Fall 2013)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>166</v>
+      </c>
+      <c r="C17" t="n">
+        <v>572</v>
+      </c>
+      <c r="D17" t="n">
+        <v>579</v>
+      </c>
+      <c r="E17" t="n">
+        <v>346</v>
+      </c>
+      <c r="F17" t="n">
+        <v>209</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>74.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Foundations of Finance (Fall 2014)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>172</v>
+      </c>
+      <c r="C18" t="n">
+        <v>646</v>
+      </c>
+      <c r="D18" t="n">
+        <v>553</v>
+      </c>
+      <c r="E18" t="n">
+        <v>317</v>
+      </c>
+      <c r="F18" t="n">
+        <v>154</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1842</v>
+      </c>
+      <c r="H18" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Foundations of Finance (Spring 2013)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>116</v>
+      </c>
+      <c r="C19" t="n">
+        <v>486</v>
+      </c>
+      <c r="D19" t="n">
+        <v>421</v>
+      </c>
+      <c r="E19" t="n">
+        <v>218</v>
+      </c>
+      <c r="F19" t="n">
+        <v>126</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1367</v>
+      </c>
+      <c r="H19" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Foundations of Finance (Spring 2014)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>91</v>
+      </c>
+      <c r="C20" t="n">
+        <v>349</v>
+      </c>
+      <c r="D20" t="n">
+        <v>405</v>
+      </c>
+      <c r="E20" t="n">
+        <v>232</v>
+      </c>
+      <c r="F20" t="n">
+        <v>128</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1205</v>
+      </c>
+      <c r="H20" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I20" t="n">
+        <v>74.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Global Governance &amp; Geopolitics (Fall 2013)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>113</v>
+      </c>
+      <c r="C21" t="n">
+        <v>326</v>
+      </c>
+      <c r="D21" t="n">
+        <v>202</v>
+      </c>
+      <c r="E21" t="n">
+        <v>107</v>
+      </c>
+      <c r="F21" t="n">
+        <v>70</v>
+      </c>
+      <c r="G21" t="n">
+        <v>818</v>
+      </c>
+      <c r="H21" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Global Governance &amp; Geopolitics (Fall 2014)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>64</v>
+      </c>
+      <c r="C22" t="n">
+        <v>229</v>
+      </c>
+      <c r="D22" t="n">
+        <v>164</v>
+      </c>
+      <c r="E22" t="n">
+        <v>79</v>
+      </c>
+      <c r="F22" t="n">
+        <v>66</v>
+      </c>
+      <c r="G22" t="n">
+        <v>602</v>
+      </c>
+      <c r="H22" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Global Governance &amp; Geopolitics (Spring 2014)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>80</v>
+      </c>
+      <c r="C23" t="n">
+        <v>260</v>
+      </c>
+      <c r="D23" t="n">
+        <v>186</v>
+      </c>
+      <c r="E23" t="n">
+        <v>103</v>
+      </c>
+      <c r="F23" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="n">
-        <v>68.09999999999999</v>
+      <c r="G23" t="n">
+        <v>689</v>
+      </c>
+      <c r="H23" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>77.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +1179,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +1189,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>344</v>
+        <v>25820</v>
       </c>
     </row>
     <row r="4">
@@ -703,7 +1199,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77.59999999999999</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +1209,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.8</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="6">
@@ -724,7 +1220,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Environmental Economics &amp; Ethics (Fall 2014)</t>
         </is>
       </c>
     </row>
@@ -736,7 +1232,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Creative Computing &amp; Culture (Spring 2014)</t>
         </is>
       </c>
     </row>
